--- a/markets/prospects/Qatar_Ecommerce_Prospects.xlsx
+++ b/markets/prospects/Qatar_Ecommerce_Prospects.xlsx
@@ -519,12 +519,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Company Phone Numbers (comma separated)</t>
+          <t>Company Phone Numbers</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Company Emails (comma separated; marketing/sales/business only)</t>
+          <t>Company Emails</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">

--- a/markets/prospects/Qatar_Ecommerce_Prospects.xlsx
+++ b/markets/prospects/Qatar_Ecommerce_Prospects.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Master Prospects'!$A$1:$J$145</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decision Makers'!$A$1:$G$176</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decision Makers'!$A$1:$G$242</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>info@iconnectqatar.com</t>
+          <t>info@iconnectqatar.com, media.iconnectqatar@gmail.com</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faisal Al Shuaibi</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>General Manager, Duhail Sports Club</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>iSpace@darwishholding.com, iSpace_Maha@darwishholding.com</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Anis Aramouni</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Head of Marketing, Darwish Holding (iSpace parent)</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Anis Aramouni</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Head of Marketing, Darwish Holding (owner of Fifty One East)</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>+97470468000, +97471670700, +97472720907, +97470318000, +97471712199, +97431356669</t>
+          <t>+97470468000, +97471670700, +97472720907, +97470318000, +97471712199, +97431356669, +97471712177</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -4082,12 +4082,12 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Dhanuka Malinga Silva</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>e-Sales Executive (e-commerce), iSpot Qatar / ABA Group</t>
         </is>
       </c>
     </row>
@@ -4944,12 +4944,12 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
+          <t>techbaywestbay@gmail.com</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/techbay-trading-and-services</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -5050,12 +5050,12 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mohamed Eskander</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>eCommerce Operation Manager, Al Majed Oud.co (group)</t>
         </is>
       </c>
     </row>
@@ -5139,19 +5139,19 @@
           <t>hello@myperfumeshop.com.au</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/myperfumeshop</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Matt Stanley</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Founder &amp; Director, My Perfume Shop Pty Ltd (operator of myperfumeshop.qa)</t>
         </is>
       </c>
     </row>
@@ -5530,12 +5530,12 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Abdul Bashar CP</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Manager - Marketing &amp; Business Development, Rafhealth (Raf Pharmacy)</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>info@aljanoubstores.com.qa</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
@@ -5722,12 +5722,12 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Asgar Ali Cherukuniyil</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Managing Director / CEO, Floranza International Nursery WLL</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Anis Aramouni</t>
         </is>
       </c>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Head of Marketing, Darwish Holding (operator of Sony World Qatar)</t>
         </is>
       </c>
     </row>
@@ -5818,12 +5818,12 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Radhika Choksey</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Head of Marketing, Brand &amp; Communications - META, Philips</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Paul Lalley</t>
         </is>
       </c>
       <c r="J111" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Founder &amp; CEO, RimRubber.com</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>info@chocolaparis.qa</t>
+          <t>info@chocolaparis.qa, chocolaparisdoha@gmail.com</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Sajeer Thaivacha Madamvally</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Co-Founder - Digital Sale (e-commerce lead), Chocola Paris</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Syed Adil Adnan</t>
         </is>
       </c>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>E-Commerce &amp; Digital Media Manager / Head of E-Commerce, Swiss Arabian Perfumes Group (group-level)</t>
         </is>
       </c>
     </row>
@@ -5997,12 +5997,12 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>+97455461026, +97444343010, +97444343030, +97444343044, +97444423378</t>
+          <t>+97455461026, +97444343010, +97444343030, +97444343044, +97444423378, +97444343000</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>info@nehmeh.com</t>
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Arun Saini</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Business Unit Manager - Makita, Nehmeh Corporation (Makita Qatar distributor)</t>
         </is>
       </c>
     </row>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mohammed Fituri</t>
         </is>
       </c>
       <c r="J115" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Co-Founder, Voltaat Store</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>info@rais.qa</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Abdul Razzak Al-Rais</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Founder, Owner and President, Al Rais Group (Generalco)</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>+97444861400</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>clients@alfardanjewellery.com</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Ali Alfardan</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>President, Alfardan Jewellery / Vice-Chairman, Alfardan Group (operator of Chopard Qatar boutiques)</t>
         </is>
       </c>
     </row>
@@ -6254,12 +6254,12 @@
       </c>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Jauhar PS</t>
         </is>
       </c>
       <c r="J119" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Regional Manager - Ecommerce, Hotpack Global (GCC incl. Qatar)</t>
         </is>
       </c>
     </row>
@@ -6385,12 +6385,12 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>+97439963232, WhatsApp +97439963232</t>
+          <t>+97439963232, WhatsApp +97439963232, +97444696700</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Info@intertecqatar.com</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Fahmi Abdulla O.P</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Business Development Manager - Ecommerce &amp; Hitech Retail, Intertec Group W.L.L.</t>
         </is>
       </c>
     </row>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mohammed Ismail Cheriya Meethalagath</t>
         </is>
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Managing Director and Founder, The Garden Centre W.L.L.</t>
         </is>
       </c>
     </row>
@@ -6496,12 +6496,12 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Nishaat Ahmed Nazeem</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Digital Media &amp; E-commerce Specialist cum Branch Manager, IMALCO (IMALCO Webstore)</t>
         </is>
       </c>
     </row>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Info@qatarvet.com</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Dr Judy Hensen</t>
         </is>
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>CEO, Qatar Veterinary Center</t>
         </is>
       </c>
     </row>
@@ -6592,12 +6592,12 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Kshitiz Saxena</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Chief Business Officer (GCC eCommerce), Ourshopee.com</t>
         </is>
       </c>
     </row>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Thasneem Ashraf CK</t>
         </is>
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>General Manager, Qmax International Trading WLL</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Jean Thomas</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>CMO &amp; Chief Product/Tech Officer (eCommerce &amp; marketing, GCC), Eyewa</t>
         </is>
       </c>
     </row>
@@ -6736,12 +6736,12 @@
       </c>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Moradeke (Dee) Ogunbiyi</t>
         </is>
       </c>
       <c r="J129" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Brand Manager, LUSH Qatar (Almana Group)</t>
         </is>
       </c>
     </row>
@@ -6825,19 +6825,19 @@
           <t>marketing@elctoys.com</t>
         </is>
       </c>
-      <c r="H131" s="5" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H131" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/early-learning-centre-middleeast</t>
         </is>
       </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Alywin Liusie</t>
         </is>
       </c>
       <c r="J131" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Executive Director, Early Learning Centre ME (ALGT, franchise operator for Qatar)</t>
         </is>
       </c>
     </row>
@@ -6880,12 +6880,12 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hasan Ebrahim</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Country Head GCC (KSA, UAE, Qatar, Bahrain), Mumzworld</t>
         </is>
       </c>
     </row>
@@ -7024,12 +7024,12 @@
       </c>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mohammad Tausif Salah</t>
         </is>
       </c>
       <c r="J135" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Head of E-Commerce, Ajmal Perfumes</t>
         </is>
       </c>
     </row>
@@ -7168,12 +7168,12 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mohamed Ehiya (M.M. Ehiya)</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Owner &amp; Chairman, Black Tulip Group</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>media@olivesuno.com</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Muhammed Bashayir</t>
         </is>
       </c>
       <c r="J139" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Head of Marketing Communications, Olive Suno Radio Network</t>
         </is>
       </c>
     </row>
@@ -7360,12 +7360,12 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Sanja Gorgieva</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Regional Brand Manager - Ted Baker (MENA), Al-Futtaim</t>
         </is>
       </c>
     </row>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>sales@startechsys.net</t>
+          <t>sales@startechsys.net, Info@startechsys.net</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Shajeer Purayil</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Business Owner / Founder &amp; MD, Star Tech Middle East WLL</t>
         </is>
       </c>
     </row>
@@ -7685,87 +7685,90 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId167"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B91" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B92" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B93" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B94" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B95" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B96" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B97" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B105" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B106" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B107" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B108" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B109" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B110" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B111" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B112" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B113" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B115" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B117" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B118" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B119" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B120" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B121" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B122" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B123" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B124" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B125" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B126" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B127" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B128" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B129" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B130" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B131" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B132" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B133" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B134" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B135" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B136" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B137" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B138" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B139" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B140" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B141" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B142" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B143" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B144" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B145" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B93" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B94" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B95" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B96" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B97" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B105" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B106" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B107" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B108" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B109" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B110" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B111" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B112" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B113" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B115" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B117" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B118" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B119" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B120" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B121" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B122" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B123" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B124" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B125" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B126" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B127" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B128" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B129" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B130" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B131" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B132" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B133" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B134" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B135" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B136" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B137" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B138" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B139" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B140" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B141" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B142" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B143" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B144" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B145" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId253"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7778,7 +7781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G176"/>
+  <dimension ref="A1:G242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -11308,22 +11311,22 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>MAGRABi Qatar</t>
+          <t>Duhail Sports Club</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>https://www.magrabi.com/qa-en/</t>
+          <t>https://www.duhailsc.qa/</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Salma Intabli</t>
+          <t>Faisal Al Shuaibi</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Director Marketing Communications (ex Head of Performance - Ecommerce), MAGRABi Retail Group</t>
+          <t>General Manager, Duhail Sports Club</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -11336,31 +11339,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G96" s="3" t="inlineStr">
-        <is>
-          <t>https://ae.linkedin.com/in/salmaintabli</t>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>MAGRABi Qatar</t>
+          <t>Duhail Sports Club</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>https://www.magrabi.com/qa-en/</t>
+          <t>https://www.duhailsc.qa/</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Peter Ayad</t>
+          <t>Adnan Al Ali</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>Digital Product Manager - E-Commerce &amp; Omnichannel, MAGRABi Retail Group</t>
+          <t>Sporting CEO / Chief Executive Officer (football), Al Duhail SC</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -11373,31 +11376,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G97" s="6" t="inlineStr">
-        <is>
-          <t>https://ae.linkedin.com/in/peter-ayad-377625104</t>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Gait Qatar (Gait MENA)</t>
+          <t>MAGRABi Qatar</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>https://gait.com.qa/</t>
+          <t>https://www.magrabi.com/qa-en/</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Nawaf Ahmed</t>
+          <t>Salma Intabli</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Regional Marketing Manager (Kuwait &amp; Qatar), Gait MENA (Apple Premium Partner)</t>
+          <t>Director Marketing Communications (ex Head of Performance - Ecommerce), MAGRABi Retail Group</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -11412,29 +11415,29 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/nawafahmed1</t>
+          <t>https://ae.linkedin.com/in/salmaintabli</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>Gait Qatar (Gait MENA)</t>
+          <t>MAGRABi Qatar</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>https://gait.com.qa/</t>
+          <t>https://www.magrabi.com/qa-en/</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Abedeen Shujauddin</t>
+          <t>Peter Ayad</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>Category Head, Gait MENA</t>
+          <t>Digital Product Manager - E-Commerce &amp; Omnichannel, MAGRABi Retail Group</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -11449,29 +11452,29 @@
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/abedeenshuja</t>
+          <t>https://ae.linkedin.com/in/peter-ayad-377625104</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Salam Stores</t>
+          <t>Gait Qatar (Gait MENA)</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>https://salams.com/</t>
+          <t>https://gait.com.qa/</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Mohamed Abu Issa</t>
+          <t>Nawaf Ahmed</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Managing Director, Salam Studio &amp; Stores</t>
+          <t>Regional Marketing Manager (Kuwait &amp; Qatar), Gait MENA (Apple Premium Partner)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -11486,29 +11489,29 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/mohamed-abu-issa-534880174</t>
+          <t>https://www.linkedin.com/in/nawafahmed1</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Salam Stores</t>
+          <t>Gait Qatar (Gait MENA)</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>https://salams.com/</t>
+          <t>https://gait.com.qa/</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>Mira Kaakani</t>
+          <t>Abedeen Shujauddin</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>Retail Marketing Manager, Salam Studio &amp; Stores</t>
+          <t>Category Head, Gait MENA</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -11523,29 +11526,29 @@
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/mira-kaakani</t>
+          <t>https://www.linkedin.com/in/abedeenshuja</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>MenaHub</t>
+          <t>Salam Stores</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>https://menahub.com/</t>
+          <t>https://salams.com/</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Prajith Krishnan</t>
+          <t>Mohamed Abu Issa</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Head of Ecommerce, MenaHub</t>
+          <t>Managing Director, Salam Studio &amp; Stores</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -11560,29 +11563,29 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/prajith-krishnan-63a726200</t>
+          <t>https://linkedin.com/in/mohamed-abu-issa-534880174</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Al Annabi Electronics</t>
+          <t>Salam Stores</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>https://alannabi.qa/</t>
+          <t>https://salams.com/</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Yasser Zain</t>
+          <t>Mira Kaakani</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>Owner / Founder, Al Annabi Electronics</t>
+          <t>Retail Marketing Manager, Salam Studio &amp; Stores</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -11595,31 +11598,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G103" s="5" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/mira-kaakani</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Al Annabi Electronics</t>
+          <t>iSpace Apple Premium Reseller in Qatar</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>https://alannabi.qa/</t>
+          <t>https://ispace.qa/</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Zainul Abdein</t>
+          <t>Anis Aramouni</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>General Manager, Al Annabi Electronics</t>
+          <t>Head of Marketing, Darwish Holding (parent of iSpace Qatar)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -11632,31 +11635,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/anis-aramouni-3254216</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>Ajmal Perfumes</t>
+          <t>iSpace Apple Premium Reseller in Qatar</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>https://en-qa.ajmal.com/</t>
+          <t>https://ispace.qa/</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Mohammad Tausif Salah</t>
+          <t>Bader Al-Darwish</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>Head of Ecommerce, Ajmal Perfumes</t>
+          <t>Chairman and Managing Director, Darwish Holding (parent of iSpace and Fifty One East)</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -11669,31 +11672,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G105" s="6" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/tausif-salah</t>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Damas Jewellery</t>
+          <t>MenaHub</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>https://www.damasjewellery.com/qa-en/</t>
+          <t>https://menahub.com/</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Shashank Shobhit</t>
+          <t>Prajith Krishnan</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Head of Ecommerce, Damas Jewellery</t>
+          <t>Head of Ecommerce, MenaHub</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -11708,29 +11711,29 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/shashank-shobhit-49579655</t>
+          <t>https://linkedin.com/in/prajith-krishnan-63a726200</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>Damas Jewellery</t>
+          <t>Al Annabi Electronics</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>https://www.damasjewellery.com/qa-en/</t>
+          <t>https://alannabi.qa/</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>Amna Omer</t>
+          <t>Yasser Zain</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>Senior Digital Marketing Lead, Damas Jewellery</t>
+          <t>Owner / Founder, Al Annabi Electronics</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -11743,31 +11746,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G107" s="6" t="inlineStr">
-        <is>
-          <t>https://ae.linkedin.com/in/amna-omer</t>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>FNP</t>
+          <t>Al Annabi Electronics</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>https://www.fnp.qa/</t>
+          <t>https://alannabi.qa/</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Mohammad Mansour</t>
+          <t>Zainul Abdein</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>General Manager Qatar, FNP Arabia (website, app, marketplaces)</t>
+          <t>General Manager, Al Annabi Electronics</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -11780,31 +11783,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G108" s="3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/mmansour1984</t>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>Bershka Qatar (Azadea)</t>
+          <t>Ajmal Perfumes</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>https://www.bershka.com/qa/</t>
+          <t>https://en-qa.ajmal.com/</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Elie Hawa</t>
+          <t>Mohammad Tausif Salah</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>Regional Head of eCommerce, Azadea Group (Inditex franchise operator for Qatar)</t>
+          <t>Head of Ecommerce, Ajmal Perfumes</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -11819,29 +11822,29 @@
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/elie-hawa-634059106</t>
+          <t>https://linkedin.com/in/tausif-salah</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Bershka Qatar (Azadea)</t>
+          <t>Damas Jewellery</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>https://www.bershka.com/qa/</t>
+          <t>https://www.damasjewellery.com/qa-en/</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Stephany Sabella</t>
+          <t>Shashank Shobhit</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Head of Marketing &amp; Business Development MENA (e-commerce &amp; offline; Zara, Massimo Dutti), Azadea Group</t>
+          <t>Head of Ecommerce, Damas Jewellery</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -11856,29 +11859,29 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/stephanysabella</t>
+          <t>https://linkedin.com/in/shashank-shobhit-49579655</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>Mothercare Qatar (Alshaya)</t>
+          <t>Damas Jewellery</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>https://www.mothercare.qa/</t>
+          <t>https://www.damasjewellery.com/qa-en/</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>Rob Silsbury</t>
+          <t>Amna Omer</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>Vice President Ecommerce, Alshaya Group (all brand websites/apps across MENA)</t>
+          <t>Senior Digital Marketing Lead, Damas Jewellery</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -11893,29 +11896,29 @@
       </c>
       <c r="G111" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/robsilsbury</t>
+          <t>https://ae.linkedin.com/in/amna-omer</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Mothercare Qatar (Alshaya)</t>
+          <t>FNP</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>https://www.mothercare.qa/</t>
+          <t>https://www.fnp.qa/</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Maëlle Mandjee (Basselot)</t>
+          <t>Mohammad Mansour</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Director of Ecommerce, Alshaya Group</t>
+          <t>General Manager Qatar, FNP Arabia (website, app, marketplaces)</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -11930,29 +11933,29 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ma%C3%ABlle-basselot</t>
+          <t>https://www.linkedin.com/in/mmansour1984</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>Mamas &amp; Papas Middle East</t>
+          <t>Bershka Qatar (Azadea)</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>https://mamasandpapas.qa/</t>
+          <t>https://www.bershka.com/qa/</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>Awatef Airan</t>
+          <t>Elie Hawa</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>Head of Product (Digital), Al Tayer Retail - Mamas &amp; Papas, Bloomingdale's, Gap</t>
+          <t>Regional Head of eCommerce, Azadea Group (Inditex franchise operator for Qatar)</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -11967,29 +11970,29 @@
       </c>
       <c r="G113" s="6" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/awatef-airan-29708a114</t>
+          <t>https://www.linkedin.com/in/elie-hawa-634059106</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Mamas &amp; Papas Middle East</t>
+          <t>Bershka Qatar (Azadea)</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>https://mamasandpapas.qa/</t>
+          <t>https://www.bershka.com/qa/</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Pragya Singh</t>
+          <t>Stephany Sabella</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketing Manager (Lifestyle brands incl. Mamas &amp; Papas, Gymshark, Gap), Al Tayer Group</t>
+          <t>Head of Marketing &amp; Business Development MENA (e-commerce &amp; offline; Zara, Massimo Dutti), Azadea Group</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -12004,29 +12007,29 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/pragya-singh-aa428b29</t>
+          <t>https://www.linkedin.com/in/stephanysabella</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>Marks &amp; Spencer</t>
+          <t>Mothercare Qatar (Alshaya)</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>https://www.marksandspencer.qa/</t>
+          <t>https://www.mothercare.qa/</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>Areej Ali</t>
+          <t>Rob Silsbury</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>Manager - Digital Trade, Marks &amp; Spencer (Al-Futtaim), led M&amp;S Qatar e-commerce launch</t>
+          <t>Vice President Ecommerce, Alshaya Group (all brand websites/apps across MENA)</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -12041,29 +12044,29 @@
       </c>
       <c r="G115" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/areejali99</t>
+          <t>https://www.linkedin.com/in/robsilsbury</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Pull&amp;Bear Qatar (Azadea)</t>
+          <t>Mothercare Qatar (Alshaya)</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>https://www.pullandbear.com/qa/</t>
+          <t>https://www.mothercare.qa/</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Elie Hawa</t>
+          <t>Maëlle Mandjee (Basselot)</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Regional Head of eCommerce, Azadea Group (Inditex franchise operator for Qatar)</t>
+          <t>Director of Ecommerce, Alshaya Group</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -12078,29 +12081,29 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/elie-hawa-634059106</t>
+          <t>https://www.linkedin.com/in/ma%C3%ABlle-basselot</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>Pull&amp;Bear Qatar (Azadea)</t>
+          <t>Mamas &amp; Papas Middle East</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>https://www.pullandbear.com/qa/</t>
+          <t>https://mamasandpapas.qa/</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>Stephany Sabella</t>
+          <t>Awatef Airan</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>Head of Marketing &amp; Business Development MENA (e-commerce &amp; offline; Zara, Massimo Dutti), Azadea Group</t>
+          <t>Head of Product (Digital), Al Tayer Retail - Mamas &amp; Papas, Bloomingdale's, Gap</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -12115,29 +12118,29 @@
       </c>
       <c r="G117" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/stephanysabella</t>
+          <t>https://linkedin.com/in/awatef-airan-29708a114</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Sun &amp; Sand Sports Qatar (GMG)</t>
+          <t>Mamas &amp; Papas Middle East</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>https://ar-qa.sssports.com/</t>
+          <t>https://mamasandpapas.qa/</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Candice de Dieuleveult</t>
+          <t>Pragya Singh</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Director of Ecommerce, GMG (Sun &amp; Sand Sports / Nike GCC e-commerce operator)</t>
+          <t>Digital Marketing Manager (Lifestyle brands incl. Mamas &amp; Papas, Gymshark, Gap), Al Tayer Group</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -12152,29 +12155,29 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/candice-de-dieuleveult-9139a0135</t>
+          <t>https://linkedin.com/in/pragya-singh-aa428b29</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>Sun &amp; Sand Sports Qatar (GMG)</t>
+          <t>Marks &amp; Spencer</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>https://ar-qa.sssports.com/</t>
+          <t>https://www.marksandspencer.qa/</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>Nickel Koshy</t>
+          <t>Areej Ali</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>Regional Category Manager Digital | Trade (sssports.com), GMG</t>
+          <t>Manager - Digital Trade, Marks &amp; Spencer (Al-Futtaim), led M&amp;S Qatar e-commerce launch</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -12189,19 +12192,19 @@
       </c>
       <c r="G119" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/nickel-koshy-b63289b7</t>
+          <t>https://www.linkedin.com/in/areejali99</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Zara Home Qatar (Azadea)</t>
+          <t>Pull&amp;Bear Qatar (Azadea)</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>https://www.zarahome.com/qa/</t>
+          <t>https://www.pullandbear.com/qa/</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -12233,12 +12236,12 @@
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>Zara Home Qatar (Azadea)</t>
+          <t>Pull&amp;Bear Qatar (Azadea)</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>https://www.zarahome.com/qa/</t>
+          <t>https://www.pullandbear.com/qa/</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
@@ -12270,22 +12273,22 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Massimo Dutti Qatar (Azadea)</t>
+          <t>Luxury Shopping in Qatar</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>https://www.massimodutti.com/qa/</t>
+          <t>https://51east.com/</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Elie Hawa</t>
+          <t>Anis Aramouni</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Regional Head of eCommerce, Azadea Group (Inditex franchise operator for Qatar)</t>
+          <t>Head of Marketing, Darwish Holding (owner of Fifty One East)</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -12300,29 +12303,29 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/elie-hawa-634059106</t>
+          <t>https://linkedin.com/in/anis-aramouni-3254216</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>Massimo Dutti Qatar (Azadea)</t>
+          <t>Luxury Shopping in Qatar</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>https://www.massimodutti.com/qa/</t>
+          <t>https://51east.com/</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>Stephany Sabella</t>
+          <t>Bader Al-Darwish</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>Head of Marketing &amp; Business Development MENA (e-commerce &amp; offline; Zara, Massimo Dutti), Azadea Group</t>
+          <t>Chairman and Managing Director, Fifty One East / Darwish Holding</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -12335,31 +12338,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G123" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/stephanysabella</t>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>QSales Qatar</t>
+          <t>Luxury Shopping in Qatar</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>https://qsales.qa/</t>
+          <t>https://51east.com/</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Muhammad Aslam</t>
+          <t>Ahmad Karaki</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Founder &amp; CEO, QSales</t>
+          <t>Multi-brands Marketing Manager, 51 East</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -12374,29 +12377,29 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>https://qa.linkedin.com/in/muhammad-aslam-99b937229</t>
+          <t>https://linkedin.com/in/ahmad-karaki-42979064</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>QSales Qatar</t>
+          <t>Sun &amp; Sand Sports Qatar (GMG)</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>https://qsales.qa/</t>
+          <t>https://ar-qa.sssports.com/</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>Munavvir Chelen</t>
+          <t>Candice de Dieuleveult</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>Co-Founder, QSales</t>
+          <t>Director of Ecommerce, GMG (Sun &amp; Sand Sports / Nike GCC e-commerce operator)</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -12409,31 +12412,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G125" s="5" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="G125" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/candice-de-dieuleveult-9139a0135</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>QSales Qatar</t>
+          <t>Sun &amp; Sand Sports Qatar (GMG)</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>https://qsales.qa/</t>
+          <t>https://ar-qa.sssports.com/</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Hashif Hamza</t>
+          <t>Nickel Koshy</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Digital Growth Manager, Qsales Online Shopping</t>
+          <t>Regional Category Manager Digital | Trade (sssports.com), GMG</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -12448,29 +12451,29 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/hashifhamza</t>
+          <t>https://www.linkedin.com/in/nickel-koshy-b63289b7</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>Al Shaheen Est</t>
+          <t>Zara Home Qatar (Azadea)</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>https://alshaheenest.com/</t>
+          <t>https://www.zarahome.com/qa/</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Ben Dreh</t>
+          <t>Elie Hawa</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>Administrative &amp; E-Commerce Manager, Al Shaheen Est</t>
+          <t>Regional Head of eCommerce, Azadea Group (Inditex franchise operator for Qatar)</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -12485,29 +12488,29 @@
       </c>
       <c r="G127" s="6" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/mohamed-ben-dreh-4325b060</t>
+          <t>https://www.linkedin.com/in/elie-hawa-634059106</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Halamama</t>
+          <t>Zara Home Qatar (Azadea)</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>https://halamama.com/</t>
+          <t>https://www.zarahome.com/qa/</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Jamil Kassam</t>
+          <t>Stephany Sabella</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Head of Trading &amp; Growth (ex Head of Marketing &amp; eCommerce), Halamama</t>
+          <t>Head of Marketing &amp; Business Development MENA (e-commerce &amp; offline; Zara, Massimo Dutti), Azadea Group</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -12522,29 +12525,29 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/jamilkassam</t>
+          <t>https://www.linkedin.com/in/stephanysabella</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>Halamama</t>
+          <t>Massimo Dutti Qatar (Azadea)</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>https://halamama.com/</t>
+          <t>https://www.massimodutti.com/qa/</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>Thahil Najfar</t>
+          <t>Elie Hawa</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>Founder &amp; CEO, Halamama</t>
+          <t>Regional Head of eCommerce, Azadea Group (Inditex franchise operator for Qatar)</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -12559,29 +12562,29 @@
       </c>
       <c r="G129" s="6" t="inlineStr">
         <is>
-          <t>https://qa.linkedin.com/in/thahil-najfar</t>
+          <t>https://www.linkedin.com/in/elie-hawa-634059106</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Panda Hypermarket Qatar</t>
+          <t>Massimo Dutti Qatar (Azadea)</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>https://panda.qa/</t>
+          <t>https://www.massimodutti.com/qa/</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Mohammed Sadiqali</t>
+          <t>Stephany Sabella</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Project Manager, Panda Group (Qatar)</t>
+          <t>Head of Marketing &amp; Business Development MENA (e-commerce &amp; offline; Zara, Massimo Dutti), Azadea Group</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -12596,29 +12599,29 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/mohammed-sadiqali-dev</t>
+          <t>https://www.linkedin.com/in/stephanysabella</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>Panda Hypermarket Qatar</t>
+          <t>QSales Qatar</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>https://panda.qa/</t>
+          <t>https://qsales.qa/</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>Bekal Mohammed Shali</t>
+          <t>Muhammad Aslam</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>Managing Director / Managing Partner, Panda Hypermarket Qatar</t>
+          <t>Founder &amp; CEO, QSales</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -12631,31 +12634,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G131" s="5" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="G131" s="6" t="inlineStr">
+        <is>
+          <t>https://qa.linkedin.com/in/muhammad-aslam-99b937229</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Panda Hypermarket Qatar</t>
+          <t>QSales Qatar</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>https://panda.qa/</t>
+          <t>https://qsales.qa/</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Kurumberi Moosa</t>
+          <t>Munavvir Chelen</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Managing Director / Managing Partner, Panda Hypermarket Qatar</t>
+          <t>Co-Founder, QSales</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -12677,22 +12680,22 @@
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>Digital Zone Qatar</t>
+          <t>QSales Qatar</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>https://digitalzone.qa/</t>
+          <t>https://qsales.qa/</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>Mansoor Edasseri</t>
+          <t>Hashif Hamza</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>Ecommerce Manager, Digital Zone Qatar</t>
+          <t>Digital Growth Manager, Qsales Online Shopping</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -12707,29 +12710,29 @@
       </c>
       <c r="G133" s="6" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/mansooredasseri</t>
+          <t>https://linkedin.com/in/hashifhamza</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Digital Zone Qatar</t>
+          <t>Al Shaheen Est</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>https://digitalzone.qa/</t>
+          <t>https://alshaheenest.com/</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Akbar Ali</t>
+          <t>Mohamed Ben Dreh</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Manager Sales &amp; Partnerships, Digital Zone Qatar</t>
+          <t>Administrative &amp; E-Commerce Manager, Al Shaheen Est</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -12742,31 +12745,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/mohamed-ben-dreh-4325b060</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>Qatar Mobile</t>
+          <t>Halamama</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>https://qatarmobile.qa/</t>
+          <t>https://halamama.com/</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>Subhash K Sudhakaran</t>
+          <t>Jamil Kassam</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>General Manager | Qatar Mobile</t>
+          <t>Head of Trading &amp; Growth (ex Head of Marketing &amp; eCommerce), Halamama</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -12781,29 +12784,29 @@
       </c>
       <c r="G135" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/subhash-k-sudhakaran-818971184</t>
+          <t>https://linkedin.com/in/jamilkassam</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GETIT.QA</t>
+          <t>Halamama</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>https://getit.qa/</t>
+          <t>https://halamama.com/</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Arjun Ramachandran</t>
+          <t>Thahil Najfar</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Manager - Sales &amp; Marketing, GETIT.QA</t>
+          <t>Founder &amp; CEO, Halamama</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -12818,29 +12821,29 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/arjun-ramachandran-a506318b</t>
+          <t>https://qa.linkedin.com/in/thahil-najfar</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>GETIT.QA</t>
+          <t>iSpot</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>https://getit.qa/</t>
+          <t>https://www.ispotaba.com/</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>Jipson Jacob</t>
+          <t>Dhanuka Malinga Silva</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>Group CEO &amp; Co-Founder, GETIT</t>
+          <t>e-Sales Executive (e-commerce), iSpot Qatar / ABA Group</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -12853,31 +12856,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G137" s="5" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="G137" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/dhanuka-malinga-silva-0b0bb6135</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GETIT.QA</t>
+          <t>Panda Hypermarket Qatar</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>https://getit.qa/</t>
+          <t>https://panda.qa/</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Siddeek Ahmed Haji P</t>
+          <t>Mohammed Sadiqali</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Chairman &amp; Managing Director, GETIT</t>
+          <t>Ecommerce Project Manager, Panda Group (Qatar)</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -12890,31 +12893,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/mohammed-sadiqali-dev</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>Stradivarius Qatar (Azadea)</t>
+          <t>Panda Hypermarket Qatar</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>https://www.stradivarius.com/qa/</t>
+          <t>https://panda.qa/</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>Elie Hawa</t>
+          <t>Bekal Mohammed Shali</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>Regional Head of eCommerce, Azadea Group (Inditex franchise operator for Qatar)</t>
+          <t>Managing Director / Managing Partner, Panda Hypermarket Qatar</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -12927,31 +12930,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G139" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/elie-hawa-634059106</t>
+      <c r="G139" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Stradivarius Qatar (Azadea)</t>
+          <t>Panda Hypermarket Qatar</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>https://www.stradivarius.com/qa/</t>
+          <t>https://panda.qa/</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Stephany Sabella</t>
+          <t>Kurumberi Moosa</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Head of Marketing &amp; Business Development MENA (e-commerce &amp; offline; Zara, Massimo Dutti), Azadea Group</t>
+          <t>Managing Director / Managing Partner, Panda Hypermarket Qatar</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -12964,31 +12967,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G140" s="3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/stephanysabella</t>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>Arabian Oud Qatar</t>
+          <t>Digital Zone Qatar</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>https://qa.arabianoud.com/</t>
+          <t>https://digitalzone.qa/</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>Ibrahim Abdelmoty</t>
+          <t>Mansoor Edasseri</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>Head of Ecommerce, Arabian Oud</t>
+          <t>Ecommerce Manager, Digital Zone Qatar</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -13003,29 +13006,29 @@
       </c>
       <c r="G141" s="6" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/ibrahim101</t>
+          <t>https://linkedin.com/in/mansooredasseri</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Danube Home</t>
+          <t>Digital Zone Qatar</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>https://www.danubehome.com/qa/</t>
+          <t>https://digitalzone.qa/</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Wilson Dsouza</t>
+          <t>Akbar Ali</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Head of Digital Marketing, Danube Home</t>
+          <t>Manager Sales &amp; Partnerships, Digital Zone Qatar</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -13038,31 +13041,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G142" s="3" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/wilson-dsouza-1bb35b2b</t>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>Danube Home</t>
+          <t>Qatar Mobile</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>https://www.danubehome.com/qa/</t>
+          <t>https://qatarmobile.qa/</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Wadan</t>
+          <t>Subhash K Sudhakaran</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>Digital Marketing Manager, Danube Home</t>
+          <t>General Manager | Qatar Mobile</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -13077,29 +13080,29 @@
       </c>
       <c r="G143" s="6" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/mohamedwadan</t>
+          <t>https://www.linkedin.com/in/subhash-k-sudhakaran-818971184</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Danube Home</t>
+          <t>GETIT.QA</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>https://www.danubehome.com/qa/</t>
+          <t>https://getit.qa/</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Sayed Habib</t>
+          <t>Arjun Ramachandran</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>CEO, Danube Home | NRF Retail Voices 2027</t>
+          <t>Manager - Sales &amp; Marketing, GETIT.QA</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -13114,29 +13117,29 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/sayedhabib</t>
+          <t>https://linkedin.com/in/arjun-ramachandran-a506318b</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>American Eagle Qatar (Alshaya)</t>
+          <t>GETIT.QA</t>
         </is>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>https://www.americaneagle.com.qa/</t>
+          <t>https://getit.qa/</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>Rob Silsbury</t>
+          <t>Jipson Jacob</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>Vice President Ecommerce, Alshaya Group (all brand websites/apps across MENA)</t>
+          <t>Group CEO &amp; Co-Founder, GETIT</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -13149,31 +13152,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G145" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/robsilsbury</t>
+      <c r="G145" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>American Eagle Qatar (Alshaya)</t>
+          <t>GETIT.QA</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>https://www.americaneagle.com.qa/</t>
+          <t>https://getit.qa/</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Maëlle Mandjee (Basselot)</t>
+          <t>Siddeek Ahmed Haji P</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Director of Ecommerce, Alshaya Group</t>
+          <t>Chairman &amp; Managing Director, GETIT</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -13186,31 +13189,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G146" s="3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/ma%C3%ABlle-basselot</t>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>Huda Beauty</t>
+          <t>Stradivarius Qatar (Azadea)</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>https://hudabeauty.com/en-qa/</t>
+          <t>https://www.stradivarius.com/qa/</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>Sandra Rodrigues</t>
+          <t>Elie Hawa</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>Senior Director of eCommerce, Huda Beauty</t>
+          <t>Regional Head of eCommerce, Azadea Group (Inditex franchise operator for Qatar)</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -13225,29 +13228,29 @@
       </c>
       <c r="G147" s="6" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/sandragrodrigues</t>
+          <t>https://www.linkedin.com/in/elie-hawa-634059106</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Huda Beauty</t>
+          <t>Stradivarius Qatar (Azadea)</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>https://hudabeauty.com/en-qa/</t>
+          <t>https://www.stradivarius.com/qa/</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Kevin Clarke</t>
+          <t>Stephany Sabella</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Global eCommerce Marketing Director, Huda Beauty</t>
+          <t>Head of Marketing &amp; Business Development MENA (e-commerce &amp; offline; Zara, Massimo Dutti), Azadea Group</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -13262,29 +13265,29 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/kevvclarke</t>
+          <t>https://www.linkedin.com/in/stephanysabella</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>JS.QA (JumboSouq)</t>
+          <t>Arabian Oud Qatar</t>
         </is>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>https://js.qa/</t>
+          <t>https://qa.arabianoud.com/</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>Pravin Joseph</t>
+          <t>Ibrahim Abdelmoty</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>Head of Ecommerce Marketplace &amp; GCC, JS.QA (JumboSouq)</t>
+          <t>Head of Ecommerce, Arabian Oud</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -13299,29 +13302,29 @@
       </c>
       <c r="G149" s="6" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/pravin-joseph-ecommerce</t>
+          <t>https://linkedin.com/in/ibrahim101</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>JS.QA (JumboSouq)</t>
+          <t>Danube Home</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>https://js.qa/</t>
+          <t>https://www.danubehome.com/qa/</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>C.V. Rappai</t>
+          <t>Wilson Dsouza</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer, JS.QA / Jumbo Electronics Qatar</t>
+          <t>Head of Digital Marketing, Danube Home</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -13334,31 +13337,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="G150" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/wilson-dsouza-1bb35b2b</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>JS.QA (JumboSouq)</t>
+          <t>Danube Home</t>
         </is>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>https://js.qa/</t>
+          <t>https://www.danubehome.com/qa/</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>Sajed Jassim Mohammed Sulaiman</t>
+          <t>Mohamed Wadan</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>Vice Chairman &amp; Managing Director, JS.QA</t>
+          <t>Digital Marketing Manager, Danube Home</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -13371,31 +13374,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G151" s="5" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="G151" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/mohamedwadan</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>PharmaCare Online</t>
+          <t>Danube Home</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>https://pharmacareonline.qa/</t>
+          <t>https://www.danubehome.com/qa/</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Fahid Azher</t>
+          <t>Sayed Habib</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Marketing Manager (leads e-commerce team), Pharmacare Group</t>
+          <t>CEO, Danube Home | NRF Retail Voices 2027</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -13410,29 +13413,29 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/fahid-azher-99161920b</t>
+          <t>https://www.linkedin.com/in/sayedhabib</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>PharmaCare Online</t>
+          <t>American Eagle Qatar (Alshaya)</t>
         </is>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>https://pharmacareonline.qa/</t>
+          <t>https://www.americaneagle.com.qa/</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>Noufal Kattayat</t>
+          <t>Rob Silsbury</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>Co-founder &amp; Managing Director, Pharma Care Group</t>
+          <t>Vice President Ecommerce, Alshaya Group (all brand websites/apps across MENA)</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -13447,29 +13450,29 @@
       </c>
       <c r="G153" s="6" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/noufal-kattayat-265b66328</t>
+          <t>https://www.linkedin.com/in/robsilsbury</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Oysho Qatar (Azadea)</t>
+          <t>American Eagle Qatar (Alshaya)</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>https://www.oysho.com/qa/</t>
+          <t>https://www.americaneagle.com.qa/</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Elie Hawa</t>
+          <t>Maëlle Mandjee (Basselot)</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Regional Head of eCommerce, Azadea Group (Inditex franchise operator for Qatar)</t>
+          <t>Director of Ecommerce, Alshaya Group</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -13484,29 +13487,29 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/elie-hawa-634059106</t>
+          <t>https://www.linkedin.com/in/ma%C3%ABlle-basselot</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>Oysho Qatar (Azadea)</t>
+          <t>Huda Beauty</t>
         </is>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>https://www.oysho.com/qa/</t>
+          <t>https://hudabeauty.com/en-qa/</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>Stephany Sabella</t>
+          <t>Sandra Rodrigues</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>Head of Marketing &amp; Business Development MENA (e-commerce &amp; offline; Zara, Massimo Dutti), Azadea Group</t>
+          <t>Senior Director of eCommerce, Huda Beauty</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -13521,29 +13524,29 @@
       </c>
       <c r="G155" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/stephanysabella</t>
+          <t>https://linkedin.com/in/sandragrodrigues</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Gamerzone Qatar</t>
+          <t>Huda Beauty</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>https://gamerzoneme.com/</t>
+          <t>https://hudabeauty.com/en-qa/</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Mohammad Hasir</t>
+          <t>Kevin Clarke</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Chief Marketing Officer, Gamerzone Qatar</t>
+          <t>Global eCommerce Marketing Director, Huda Beauty</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -13553,34 +13556,34 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>marketing@gamerzoneme.com</t>
-        </is>
-      </c>
-      <c r="G156" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/kevvclarke</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>Mosafer</t>
+          <t>JS.QA (JumboSouq)</t>
         </is>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>https://www.mosafer.com/</t>
+          <t>https://js.qa/</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>Hosam Ibrahim</t>
+          <t>Pravin Joseph</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>General Manager at Mosafer Trading</t>
+          <t>Head of Ecommerce Marketplace &amp; GCC, JS.QA (JumboSouq)</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -13595,29 +13598,29 @@
       </c>
       <c r="G157" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/hosam-ibrahim-58062a4a</t>
+          <t>https://linkedin.com/in/pravin-joseph-ecommerce</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Matalan Qatar</t>
+          <t>JS.QA (JumboSouq)</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>https://www.matalanme.com/qa_ar/</t>
+          <t>https://js.qa/</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Hasit Kakkad</t>
+          <t>C.V. Rappai</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>General Manager, BTC Fashion (Matalan, Miniso, Superdry, Balabala franchise operator)</t>
+          <t>Chief Executive Officer, JS.QA / Jumbo Electronics Qatar</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -13630,31 +13633,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G158" s="3" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/hasit-kakkad-1a47a725</t>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>Al Nasser Qatar (Alrasheed Alaalmia For Trading)</t>
+          <t>JS.QA (JumboSouq)</t>
         </is>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>https://qa.alnasser.net/</t>
+          <t>https://js.qa/</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>Fayssal Jilani</t>
+          <t>Sajed Jassim Mohammed Sulaiman</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>Group Ecommerce Manager, Al Nasser (Faisal Al Rasheed Group; KW, QA, BH, KSA, IQ, EG, PK)</t>
+          <t>Vice Chairman &amp; Managing Director, JS.QA</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -13667,31 +13670,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G159" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/fayssaljilani</t>
+      <c r="G159" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Al Nasser Qatar (Alrasheed Alaalmia For Trading)</t>
+          <t>PharmaCare Online</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>https://qa.alnasser.net/</t>
+          <t>https://pharmacareonline.qa/</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Yousef Faisal Al Rashid</t>
+          <t>Fahid Azher</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Group CEO, Al Nasser</t>
+          <t>Marketing Manager (leads e-commerce team), Pharmacare Group</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -13704,31 +13707,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="G160" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/fahid-azher-99161920b</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>VogaCloset</t>
+          <t>PharmaCare Online</t>
         </is>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>https://vogacloset.com/qatar/</t>
+          <t>https://pharmacareonline.qa/</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>Hanin Hamarneh</t>
+          <t>Noufal Kattayat</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>Founder &amp; CEO, VogaCloset</t>
+          <t>Co-founder &amp; Managing Director, Pharma Care Group</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -13743,29 +13746,29 @@
       </c>
       <c r="G161" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/hanin-hamarneh-05813a1a</t>
+          <t>https://linkedin.com/in/noufal-kattayat-265b66328</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Cole Haan Qatar (Blue Salon / Abu Issa Holding)</t>
+          <t>Oysho Qatar (Azadea)</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>https://colehaan.qa/</t>
+          <t>https://www.oysho.com/qa/</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Shahid Raufi</t>
+          <t>Elie Hawa</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Manager, Blue Salon</t>
+          <t>Regional Head of eCommerce, Azadea Group (Inditex franchise operator for Qatar)</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -13778,31 +13781,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="G162" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/elie-hawa-634059106</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>Cole Haan Qatar (Blue Salon / Abu Issa Holding)</t>
+          <t>Oysho Qatar (Azadea)</t>
         </is>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>https://colehaan.qa/</t>
+          <t>https://www.oysho.com/qa/</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>Fawaz Idrissi</t>
+          <t>Stephany Sabella</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>CEO, Blue Salon; Senior Vice President, Abu Issa Holding; Director, Starlink</t>
+          <t>Head of Marketing &amp; Business Development MENA (e-commerce &amp; offline; Zara, Massimo Dutti), Azadea Group</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -13817,29 +13820,29 @@
       </c>
       <c r="G163" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/fawaz-idrissi-a6a3734</t>
+          <t>https://www.linkedin.com/in/stephanysabella</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Riva Fashion</t>
+          <t>Gamerzone Qatar</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>https://www.rivafashion.com/en-qa/</t>
+          <t>https://gamerzoneme.com/</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Haifa Zawahreh</t>
+          <t>Mohammad Hasir</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Head of Digital Growth, Armada Retail Concept (owner of RIVA)</t>
+          <t>Chief Marketing Officer, Gamerzone Qatar</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -13849,7 +13852,7 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>marketing@gamerzoneme.com</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -13861,22 +13864,22 @@
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>Charles &amp; Keith</t>
+          <t>Mosafer</t>
         </is>
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>https://www.charleskeith.qa/</t>
+          <t>https://www.mosafer.com/</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>Plama Spetsova</t>
+          <t>Hosam Ibrahim</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>General Manager, Digital Commerce &amp; Technology, Apparel Group</t>
+          <t>General Manager at Mosafer Trading</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -13891,29 +13894,29 @@
       </c>
       <c r="G165" s="6" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/plama-spetsova</t>
+          <t>https://www.linkedin.com/in/hosam-ibrahim-58062a4a</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Charles &amp; Keith</t>
+          <t>Matalan Qatar</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>https://www.charleskeith.qa/</t>
+          <t>https://www.matalanme.com/qa_ar/</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Nisrine Zibara</t>
+          <t>Hasit Kakkad</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Regional Brand Marketing Manager - Charles &amp; Keith and Pedro (UAE, KSA, Qatar, Bahrain, Oman &amp; Kuwait), Apparel Group</t>
+          <t>General Manager, BTC Fashion (Matalan, Miniso, Superdry, Balabala franchise operator)</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -13928,29 +13931,29 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/nisrine-zibara-989366120</t>
+          <t>https://linkedin.com/in/hasit-kakkad-1a47a725</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>Muji</t>
+          <t>Al Nasser Qatar (Alrasheed Alaalmia For Trading)</t>
         </is>
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>https://www.muji.qa/</t>
+          <t>https://qa.alnasser.net/</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>Rob Silsbury</t>
+          <t>Fayssal Jilani</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>Vice President Ecommerce, Alshaya Group (all brand websites/apps across MENA)</t>
+          <t>Group Ecommerce Manager, Al Nasser (Faisal Al Rasheed Group; KW, QA, BH, KSA, IQ, EG, PK)</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -13965,29 +13968,29 @@
       </c>
       <c r="G167" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/robsilsbury</t>
+          <t>https://www.linkedin.com/in/fayssaljilani</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Muji</t>
+          <t>Al Nasser Qatar (Alrasheed Alaalmia For Trading)</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>https://www.muji.qa/</t>
+          <t>https://qa.alnasser.net/</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Farid Khan</t>
+          <t>Yousef Faisal Al Rashid</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Operations Manager Qatar (NEXT, MUJI, Claire's, Disney), Alshaya Group</t>
+          <t>Group CEO, Al Nasser</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -14000,31 +14003,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G168" s="3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/farid-khan-b86b8524</t>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>Naaz Store</t>
+          <t>Al Majed 4 Oud Qatar</t>
         </is>
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>https://naaz.qa/</t>
+          <t>https://qa.almajed4oud.com/</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>Mahmood Sayed</t>
+          <t>Mohamed Eskander</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>Managing Director at NAAZ STORE</t>
+          <t>eCommerce Operation Manager, Al Majed Oud.co (group e-commerce, Riyadh HQ; covers Qatar site)</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -14039,29 +14042,29 @@
       </c>
       <c r="G169" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/mahmood-sayed-11a06a340</t>
+          <t>https://linkedin.com/in/mohammed-eskander</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Vulcan Coffee Roastery</t>
+          <t>Al Majed 4 Oud Qatar</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>https://www.vulcanroastery.com/</t>
+          <t>https://qa.almajed4oud.com/</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Ayed Adwan</t>
+          <t>Ibrahim Sulaiman Alafif</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Co-Owner at Vulcan Coffee Roastery</t>
+          <t>General Manager of Marketing, Al Majed Oud.co (group, Riyadh HQ)</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -14076,29 +14079,29 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ayed-adwan-8b530456</t>
+          <t>https://linkedin.com/in/ibrahimalafif</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>Top Performance</t>
+          <t>Al Majed 4 Oud Qatar</t>
         </is>
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>https://topperformance.qa/</t>
+          <t>https://qa.almajed4oud.com/</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>Yousef Najem</t>
+          <t>Waleed Khaled Al Majed</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>General Manager at Top Performance Qatar</t>
+          <t>Managing Director and CEO, Al Majed for Oud</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -14111,31 +14114,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G171" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/yousef-najem</t>
+      <c r="G171" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Tawreed</t>
+          <t>Al Majed 4 Oud Qatar</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>https://tawreed.qa/</t>
+          <t>https://qa.almajed4oud.com/</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Nasser K. Al Hamar</t>
+          <t>Abdul Rahman Khaled Al Majed</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Founder, Tawreed (Alpina Group)</t>
+          <t>Chief Sales, Marketing and International Operations Officer, Al Majed for Oud</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -14157,22 +14160,22 @@
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>Chloe</t>
+          <t>My Perfume Shop</t>
         </is>
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>https://www.chloe.com/en-qa/</t>
+          <t>https://www.myperfumeshop.qa/</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>Nagi Azar</t>
+          <t>Matt Stanley</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>Commercial Manager Middle East (Retail &amp; Wholesale), Chloé - Richemont</t>
+          <t>Founder &amp; Director, My Perfume Shop (operator of myperfumeshop.qa)</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
@@ -14187,29 +14190,29 @@
       </c>
       <c r="G173" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/nagi-azar-a1b88599</t>
+          <t>https://au.linkedin.com/in/mattstanleyau</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Gymshark</t>
+          <t>My Perfume Shop</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>https://www.gymshark.qa/</t>
+          <t>https://www.myperfumeshop.qa/</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Sumit Srivastava</t>
+          <t>Mikaela Stanley</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>VP, CDO - Omnichannel Digital Innovation (Luxury Retail and Lifestyle), Al Tayer Insignia</t>
+          <t>Co-Chief Executive Officer, My Perfume Shop</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -14222,31 +14225,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G174" s="3" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/sumitsrivastavaglobal</t>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>Gymshark</t>
+          <t>VogaCloset</t>
         </is>
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>https://www.gymshark.qa/</t>
+          <t>https://vogacloset.com/qatar/</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>Pragya Singh</t>
+          <t>Hanin Hamarneh</t>
         </is>
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>Digital Marketing Manager (Mamas &amp; Papas, Gymshark, Gap), Al Tayer Group</t>
+          <t>Founder &amp; CEO, VogaCloset</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
@@ -14261,49 +14264,2491 @@
       </c>
       <c r="G175" s="6" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/pragya-singh-aa428b29</t>
+          <t>https://www.linkedin.com/in/hanin-hamarneh-05813a1a</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
+          <t>Cole Haan Qatar (Blue Salon / Abu Issa Holding)</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>https://colehaan.qa/</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Shahid Raufi</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Ecommerce Manager, Blue Salon</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="5" t="inlineStr">
+        <is>
+          <t>Cole Haan Qatar (Blue Salon / Abu Issa Holding)</t>
+        </is>
+      </c>
+      <c r="B177" s="6" t="inlineStr">
+        <is>
+          <t>https://colehaan.qa/</t>
+        </is>
+      </c>
+      <c r="C177" s="5" t="inlineStr">
+        <is>
+          <t>Fawaz Idrissi</t>
+        </is>
+      </c>
+      <c r="D177" s="5" t="inlineStr">
+        <is>
+          <t>CEO, Blue Salon; Senior Vice President, Abu Issa Holding; Director, Starlink</t>
+        </is>
+      </c>
+      <c r="E177" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F177" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G177" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fawaz-idrissi-a6a3734</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Riva Fashion</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>https://www.rivafashion.com/en-qa/</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Haifa Zawahreh</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Head of Digital Growth, Armada Retail Concept (owner of RIVA)</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="inlineStr">
+        <is>
+          <t>Charles &amp; Keith</t>
+        </is>
+      </c>
+      <c r="B179" s="6" t="inlineStr">
+        <is>
+          <t>https://www.charleskeith.qa/</t>
+        </is>
+      </c>
+      <c r="C179" s="5" t="inlineStr">
+        <is>
+          <t>Plama Spetsova</t>
+        </is>
+      </c>
+      <c r="D179" s="5" t="inlineStr">
+        <is>
+          <t>General Manager, Digital Commerce &amp; Technology, Apparel Group</t>
+        </is>
+      </c>
+      <c r="E179" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F179" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G179" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/plama-spetsova</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Charles &amp; Keith</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>https://www.charleskeith.qa/</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Nisrine Zibara</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Regional Brand Marketing Manager - Charles &amp; Keith and Pedro (UAE, KSA, Qatar, Bahrain, Oman &amp; Kuwait), Apparel Group</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G180" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/nisrine-zibara-989366120</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="5" t="inlineStr">
+        <is>
+          <t>Raf Pharmacy</t>
+        </is>
+      </c>
+      <c r="B181" s="6" t="inlineStr">
+        <is>
+          <t>https://rafpharmacy.com/</t>
+        </is>
+      </c>
+      <c r="C181" s="5" t="inlineStr">
+        <is>
+          <t>Abdul Bashar CP</t>
+        </is>
+      </c>
+      <c r="D181" s="5" t="inlineStr">
+        <is>
+          <t>Manager - Marketing &amp; Business Development, Rafhealth (Raf Pharmacy)</t>
+        </is>
+      </c>
+      <c r="E181" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F181" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G181" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/abdul-bashar-cp-40a739153</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Raf Pharmacy</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>https://rafpharmacy.com/</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>Aathif Asharaf</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director, Rafhealth (Raf Pharmacy)</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G182" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/aathif-asharaf-0948a2263</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="5" t="inlineStr">
+        <is>
+          <t>Raf Pharmacy</t>
+        </is>
+      </c>
+      <c r="B183" s="6" t="inlineStr">
+        <is>
+          <t>https://rafpharmacy.com/</t>
+        </is>
+      </c>
+      <c r="C183" s="5" t="inlineStr">
+        <is>
+          <t>Ashraf K.P</t>
+        </is>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
+        <is>
+          <t>Chairperson, Rafhealth (Raf Pharmacy)</t>
+        </is>
+      </c>
+      <c r="E183" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F183" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G183" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/ashrafkp</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>FLORANZA INTERNATIONAL NURSERY</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>https://floranza.qa/</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>Asgar Ali Cherukuniyil</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director / CEO, Floranza International Nursery WLL</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="5" t="inlineStr">
+        <is>
+          <t>Sony World - Qatar</t>
+        </is>
+      </c>
+      <c r="B185" s="6" t="inlineStr">
+        <is>
+          <t>https://sonyworld.qa/</t>
+        </is>
+      </c>
+      <c r="C185" s="5" t="inlineStr">
+        <is>
+          <t>Anis Aramouni</t>
+        </is>
+      </c>
+      <c r="D185" s="5" t="inlineStr">
+        <is>
+          <t>Head of Marketing, Darwish Holding (operator of Sony World Qatar)</t>
+        </is>
+      </c>
+      <c r="E185" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F185" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G185" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/anis-aramouni-3254216</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Sony World - Qatar</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>https://sonyworld.qa/</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>Sameer Kazi</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>Head - Consumer Electronics Division (Sony, Hisense...), Darwish Holding</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G186" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/sameer-kazi-10735534</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="5" t="inlineStr">
+        <is>
+          <t>Sony World - Qatar</t>
+        </is>
+      </c>
+      <c r="B187" s="6" t="inlineStr">
+        <is>
+          <t>https://sonyworld.qa/</t>
+        </is>
+      </c>
+      <c r="C187" s="5" t="inlineStr">
+        <is>
+          <t>Patrick Boustany</t>
+        </is>
+      </c>
+      <c r="D187" s="5" t="inlineStr">
+        <is>
+          <t>Brand Manager - Electronics Division, Darwish Holding (develops brand e-commerce/website marketing)</t>
+        </is>
+      </c>
+      <c r="E187" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F187" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G187" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/patrickboustany</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>https://www.philips.com.qa/</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>Radhika Choksey</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>Head of Marketing, Brand &amp; Communications - Middle East, Turkey &amp; Africa, Philips</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G188" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/radhika-choksey-a494386</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="5" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="B189" s="6" t="inlineStr">
+        <is>
+          <t>https://www.philips.com.qa/</t>
+        </is>
+      </c>
+      <c r="C189" s="5" t="inlineStr">
+        <is>
+          <t>Ahmed R.</t>
+        </is>
+      </c>
+      <c r="D189" s="5" t="inlineStr">
+        <is>
+          <t>Senior Trade Marketing Officer, Philips Domestic Appliances (Doha)</t>
+        </is>
+      </c>
+      <c r="E189" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F189" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G189" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/ahmed-r-4570b656</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>RimRubber.qa</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>https://rimrubber.qa/</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>Paul Lalley</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; CEO, RimRubber.com (RimRubber.qa)</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="5" t="inlineStr">
+        <is>
+          <t>Chocola Paris</t>
+        </is>
+      </c>
+      <c r="B191" s="6" t="inlineStr">
+        <is>
+          <t>https://chocolaparis.qa/</t>
+        </is>
+      </c>
+      <c r="C191" s="5" t="inlineStr">
+        <is>
+          <t>Sajeer Thaivacha Madamvally</t>
+        </is>
+      </c>
+      <c r="D191" s="5" t="inlineStr">
+        <is>
+          <t>Co-Founder - Digital Sale (e-commerce lead), Chocola Paris</t>
+        </is>
+      </c>
+      <c r="E191" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F191" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G191" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/sajeer-thaivacha-madamvally-b67415ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Chocola Paris</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>https://chocolaparis.qa/</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>Muhammed Shammas</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Head of Marketing, Chocola Paris (Qatar &amp; UAE)</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G192" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/muhammed-shammas-896083219</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="5" t="inlineStr">
+        <is>
+          <t>Chocola Paris</t>
+        </is>
+      </c>
+      <c r="B193" s="6" t="inlineStr">
+        <is>
+          <t>https://chocolaparis.qa/</t>
+        </is>
+      </c>
+      <c r="C193" s="5" t="inlineStr">
+        <is>
+          <t>Muhammed Hashim M K</t>
+        </is>
+      </c>
+      <c r="D193" s="5" t="inlineStr">
+        <is>
+          <t>Manager, Chocola Paris</t>
+        </is>
+      </c>
+      <c r="E193" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F193" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G193" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/muhammed-hashim-m-k-596861252</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Swiss Arabian Qatar</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>https://qa.swissarabian.com/</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>Syed Adil Adnan</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>E-Commerce &amp; Digital Media Manager / Head of E-Commerce, Swiss Arabian Perfumes Group (group-level, Sharjah HQ)</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G194" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/syedadiladnan</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="5" t="inlineStr">
+        <is>
+          <t>Swiss Arabian Qatar</t>
+        </is>
+      </c>
+      <c r="B195" s="6" t="inlineStr">
+        <is>
+          <t>https://qa.swissarabian.com/</t>
+        </is>
+      </c>
+      <c r="C195" s="5" t="inlineStr">
+        <is>
+          <t>Alia Adam Ali</t>
+        </is>
+      </c>
+      <c r="D195" s="5" t="inlineStr">
+        <is>
+          <t>Marketing and Communications Manager, Swiss Arabian Perfumes Group (group-level)</t>
+        </is>
+      </c>
+      <c r="E195" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F195" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G195" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/alianabeel</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Swiss Arabian Qatar</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>https://qa.swissarabian.com/</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>Nabeel Adam Ali</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>CEO &amp; Director, Swiss Arabian Perfumes Group</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="5" t="inlineStr">
+        <is>
+          <t>Makita | Qatar’s #1 Choice for Power Tools</t>
+        </is>
+      </c>
+      <c r="B197" s="6" t="inlineStr">
+        <is>
+          <t>https://makita.qa/</t>
+        </is>
+      </c>
+      <c r="C197" s="5" t="inlineStr">
+        <is>
+          <t>Arun Saini</t>
+        </is>
+      </c>
+      <c r="D197" s="5" t="inlineStr">
+        <is>
+          <t>Business Unit Manager - Makita (formerly Brand Manager), Nehmeh (Makita Qatar distributor)</t>
+        </is>
+      </c>
+      <c r="E197" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F197" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G197" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/arun-saini-b6b56a91</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Voltaat</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>https://www.voltaat.com/</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>Mohammed Fituri</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder, Voltaat Store</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G198" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/mfituri</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="5" t="inlineStr">
+        <is>
+          <t>Voltaat</t>
+        </is>
+      </c>
+      <c r="B199" s="6" t="inlineStr">
+        <is>
+          <t>https://www.voltaat.com/</t>
+        </is>
+      </c>
+      <c r="C199" s="5" t="inlineStr">
+        <is>
+          <t>Ahmed Yousef</t>
+        </is>
+      </c>
+      <c r="D199" s="5" t="inlineStr">
+        <is>
+          <t>Product Development Manager (merchandising, sourcing, sales growth), Voltaat Store</t>
+        </is>
+      </c>
+      <c r="E199" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F199" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G199" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/ahmed-yousef-991029202</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Generalco</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>https://generalco.qa/</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>Abdul Razzak Al-Rais</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>Founder, Owner and President, Al Rais Group (Generalco)</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="5" t="inlineStr">
+        <is>
+          <t>Generalco</t>
+        </is>
+      </c>
+      <c r="B201" s="6" t="inlineStr">
+        <is>
+          <t>https://generalco.qa/</t>
+        </is>
+      </c>
+      <c r="C201" s="5" t="inlineStr">
+        <is>
+          <t>Usman Farid</t>
+        </is>
+      </c>
+      <c r="D201" s="5" t="inlineStr">
+        <is>
+          <t>Director of Customer Experience &amp; Operations, Generalco (Al-Rais Group)</t>
+        </is>
+      </c>
+      <c r="E201" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F201" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G201" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/usman-farid-97811515</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Muji</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>https://www.muji.qa/</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>Rob Silsbury</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>Vice President Ecommerce, Alshaya Group (all brand websites/apps across MENA)</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G202" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/robsilsbury</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="5" t="inlineStr">
+        <is>
+          <t>Muji</t>
+        </is>
+      </c>
+      <c r="B203" s="6" t="inlineStr">
+        <is>
+          <t>https://www.muji.qa/</t>
+        </is>
+      </c>
+      <c r="C203" s="5" t="inlineStr">
+        <is>
+          <t>Farid Khan</t>
+        </is>
+      </c>
+      <c r="D203" s="5" t="inlineStr">
+        <is>
+          <t>Operations Manager Qatar (NEXT, MUJI, Claire's, Disney), Alshaya Group</t>
+        </is>
+      </c>
+      <c r="E203" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F203" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G203" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/farid-khan-b86b8524</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Chopard®</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>https://www.chopard.com/en-qa/</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>Ali Alfardan</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>Vice-Chairman of Alfardan Group and President of Alfardan Jewellery (Chopard partner/operator in Qatar)</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="5" t="inlineStr">
+        <is>
+          <t>hotpack.qa</t>
+        </is>
+      </c>
+      <c r="B205" s="6" t="inlineStr">
+        <is>
+          <t>https://hotpack.qa/</t>
+        </is>
+      </c>
+      <c r="C205" s="5" t="inlineStr">
+        <is>
+          <t>Jauhar PS</t>
+        </is>
+      </c>
+      <c r="D205" s="5" t="inlineStr">
+        <is>
+          <t>Regional Manager - Ecommerce (Heading Ecommerce), Hotpack Global (GCC incl. Qatar)</t>
+        </is>
+      </c>
+      <c r="E205" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F205" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G205" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/jauharps</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>hotpack.qa</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>https://hotpack.qa/</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>Arif Mohamed</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>Ecommerce Country Coordinator (Qatar), Hotpack Global</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>+97431219758</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>arifmohamed@live.com</t>
+        </is>
+      </c>
+      <c r="G206" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/arif-mohamed-781617191</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="5" t="inlineStr">
+        <is>
+          <t>Intertec Group W.L.L.</t>
+        </is>
+      </c>
+      <c r="B207" s="6" t="inlineStr">
+        <is>
+          <t>https://shopintertec.com/</t>
+        </is>
+      </c>
+      <c r="C207" s="5" t="inlineStr">
+        <is>
+          <t>Fahmi Abdulla O.P</t>
+        </is>
+      </c>
+      <c r="D207" s="5" t="inlineStr">
+        <is>
+          <t>Business Development Manager - Ecommerce &amp; Hitech Retail, Intertec Group W.L.L.</t>
+        </is>
+      </c>
+      <c r="E207" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F207" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G207" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/opfahmiabdulla</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>Intertec Group W.L.L.</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>https://shopintertec.com/</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>George Thomas</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>CEO (also Group General Manager), Intertec Group W.L.L.</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G208" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/george-thomas-743a9562</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="5" t="inlineStr">
+        <is>
+          <t>Intertec Group W.L.L.</t>
+        </is>
+      </c>
+      <c r="B209" s="6" t="inlineStr">
+        <is>
+          <t>https://shopintertec.com/</t>
+        </is>
+      </c>
+      <c r="C209" s="5" t="inlineStr">
+        <is>
+          <t>Erkin Raphael Miranda</t>
+        </is>
+      </c>
+      <c r="D209" s="5" t="inlineStr">
+        <is>
+          <t>Digital Marketing Executive (Group Digital Marketing), Intertec Group W.L.L.</t>
+        </is>
+      </c>
+      <c r="E209" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F209" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G209" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/erkin-raphael-miranda-949b7aa4</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>THE GARDEN CENTRE</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t>https://garden.qa/</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>Mohammed Ismail Cheriya Meethalagath</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director and Founder, The Garden Centre W.L.L.</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G210" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/mohammed-ismail-cheriya-meethalagath-7a747248</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="5" t="inlineStr">
+        <is>
+          <t>THE GARDEN CENTRE</t>
+        </is>
+      </c>
+      <c r="B211" s="6" t="inlineStr">
+        <is>
+          <t>https://garden.qa/</t>
+        </is>
+      </c>
+      <c r="C211" s="5" t="inlineStr">
+        <is>
+          <t>Aadil Ismail</t>
+        </is>
+      </c>
+      <c r="D211" s="5" t="inlineStr">
+        <is>
+          <t>Head of Operations (modern marketing strategy), The Garden Centre W.L.L.</t>
+        </is>
+      </c>
+      <c r="E211" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F211" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G211" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/aadil-ismail</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>IMALCO Webstore</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t>https://www.imalcowebstore.com/</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>Nishaat Ahmed Nazeem</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>Digital Media &amp; E-commerce Specialist cum Branch Manager (Customer Service), IMALCO</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G212" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/nishaatn</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="5" t="inlineStr">
+        <is>
+          <t>IMALCO Webstore</t>
+        </is>
+      </c>
+      <c r="B213" s="6" t="inlineStr">
+        <is>
+          <t>https://www.imalcowebstore.com/</t>
+        </is>
+      </c>
+      <c r="C213" s="5" t="inlineStr">
+        <is>
+          <t>Aboo Backer Bavu</t>
+        </is>
+      </c>
+      <c r="D213" s="5" t="inlineStr">
+        <is>
+          <t>CEO, IMALCO (Ibrahim Mohd. Al-Khulaifi Trading Co.)</t>
+        </is>
+      </c>
+      <c r="E213" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F213" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G213" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>Qatar Vet Center</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
+          <t>https://www.qvcpetshop.com/</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>Dr Judy Hensen</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>CEO, Qatar Veterinary Center (Qatar Vet Center)</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="5" t="inlineStr">
+        <is>
+          <t>Ourshopee</t>
+        </is>
+      </c>
+      <c r="B215" s="6" t="inlineStr">
+        <is>
+          <t>https://ourshopee.com/qatar-en/</t>
+        </is>
+      </c>
+      <c r="C215" s="5" t="inlineStr">
+        <is>
+          <t>Kshitiz Saxena</t>
+        </is>
+      </c>
+      <c r="D215" s="5" t="inlineStr">
+        <is>
+          <t>Chief Business Officer (leads GCC eCommerce business &amp; P&amp;L), Ourshopee.com</t>
+        </is>
+      </c>
+      <c r="E215" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F215" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G215" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/kshitiz</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>Ourshopee</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>https://ourshopee.com/qatar-en/</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>Parichay Tayal</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>Head of Marketing, Ourshopee.com (Qatar, Kuwait, UAE, Oman, Bahrain, KSA)</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G216" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/parichaytayal</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="5" t="inlineStr">
+        <is>
+          <t>Ourshopee</t>
+        </is>
+      </c>
+      <c r="B217" s="6" t="inlineStr">
+        <is>
+          <t>https://ourshopee.com/qatar-en/</t>
+        </is>
+      </c>
+      <c r="C217" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Shanith Mangalat</t>
+        </is>
+      </c>
+      <c r="D217" s="5" t="inlineStr">
+        <is>
+          <t>Founder &amp; Chairman, Ourshopee (DRS Holding)</t>
+        </is>
+      </c>
+      <c r="E217" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F217" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G217" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>Qmax Qatar</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>https://qmax.qa/</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>Thasneem Ashraf CK</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>General Manager, Qmax International Trading WLL (Qmax Qatar)</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G218" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/thasneem-ashraf-ck</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="5" t="inlineStr">
+        <is>
+          <t>Eyewa</t>
+        </is>
+      </c>
+      <c r="B219" s="6" t="inlineStr">
+        <is>
+          <t>https://eyewa.com/qa-en/</t>
+        </is>
+      </c>
+      <c r="C219" s="5" t="inlineStr">
+        <is>
+          <t>Jean Thomas</t>
+        </is>
+      </c>
+      <c r="D219" s="5" t="inlineStr">
+        <is>
+          <t>CMO &amp; Chief Product/Tech Officer (marketing, eCommerce, product, tech - all GCC), Eyewa</t>
+        </is>
+      </c>
+      <c r="E219" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F219" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G219" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/jeanthomasfr</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>Eyewa</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>https://eyewa.com/qa-en/</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>Anass Boumediene</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>Co-CEO &amp; Co-Founder, Eyewa</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G220" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/boumediene</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="5" t="inlineStr">
+        <is>
+          <t>Eyewa</t>
+        </is>
+      </c>
+      <c r="B221" s="6" t="inlineStr">
+        <is>
+          <t>https://eyewa.com/qa-en/</t>
+        </is>
+      </c>
+      <c r="C221" s="5" t="inlineStr">
+        <is>
+          <t>Mehdi Oudghiri</t>
+        </is>
+      </c>
+      <c r="D221" s="5" t="inlineStr">
+        <is>
+          <t>Co-CEO &amp; Co-Founder, Eyewa</t>
+        </is>
+      </c>
+      <c r="E221" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F221" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G221" s="6" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/in/mehdioudghiri</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>Lush Qatar</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>https://lush.qa/</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>Moradeke (Dee) Ogunbiyi</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager, LUSH Qatar (Almana Group), Doha</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G222" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/moradeke-dee-ogunbiyi-695a0720</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="5" t="inlineStr">
+        <is>
+          <t>Lush Qatar</t>
+        </is>
+      </c>
+      <c r="B223" s="6" t="inlineStr">
+        <is>
+          <t>https://lush.qa/</t>
+        </is>
+      </c>
+      <c r="C223" s="5" t="inlineStr">
+        <is>
+          <t>Miche Whitehouse</t>
+        </is>
+      </c>
+      <c r="D223" s="5" t="inlineStr">
+        <is>
+          <t>Regional Brand and Digital Manager - MENA, LUSH Fresh Handmade Cosmetics</t>
+        </is>
+      </c>
+      <c r="E223" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F223" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G223" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/miche-whitehouse-0534555a</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>Naaz Store</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>https://naaz.qa/</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>Mahmood Sayed</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director at NAAZ STORE</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G224" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mahmood-sayed-11a06a340</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="5" t="inlineStr">
+        <is>
+          <t>ELC Toys Qatar</t>
+        </is>
+      </c>
+      <c r="B225" s="6" t="inlineStr">
+        <is>
+          <t>https://elctoys.qa/</t>
+        </is>
+      </c>
+      <c r="C225" s="5" t="inlineStr">
+        <is>
+          <t>Alywin Liusie</t>
+        </is>
+      </c>
+      <c r="D225" s="5" t="inlineStr">
+        <is>
+          <t>Executive Director, Early Learning Centre ME / Partner &amp; Exec Director, ALGT Middle East</t>
+        </is>
+      </c>
+      <c r="E225" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F225" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G225" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/alywin-liusie-71a97a96</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>Mumzworld</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mumzworld.com/qa-en/</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>Massimiliano Spalazzi</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>Group CEO, Mumzworld</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G226" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/massimilianospalazzi</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="5" t="inlineStr">
+        <is>
+          <t>Mumzworld</t>
+        </is>
+      </c>
+      <c r="B227" s="6" t="inlineStr">
+        <is>
+          <t>https://www.mumzworld.com/qa-en/</t>
+        </is>
+      </c>
+      <c r="C227" s="5" t="inlineStr">
+        <is>
+          <t>Chirin Khawatmi</t>
+        </is>
+      </c>
+      <c r="D227" s="5" t="inlineStr">
+        <is>
+          <t>Chief Brand Officer, Mumzworld; Managing Director, Andador</t>
+        </is>
+      </c>
+      <c r="E227" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F227" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G227" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/chirin-khawatmi</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>Mumzworld</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mumzworld.com/qa-en/</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>Hasan Ebrahim</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>Country Head (GCC: KSA, UAE, Qatar, Bahrain), Mumzworld</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G228" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/h89ebrahim</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="5" t="inlineStr">
+        <is>
+          <t>Vulcan Coffee Roastery</t>
+        </is>
+      </c>
+      <c r="B229" s="6" t="inlineStr">
+        <is>
+          <t>https://www.vulcanroastery.com/</t>
+        </is>
+      </c>
+      <c r="C229" s="5" t="inlineStr">
+        <is>
+          <t>Ayed Adwan</t>
+        </is>
+      </c>
+      <c r="D229" s="5" t="inlineStr">
+        <is>
+          <t>Co-Owner at Vulcan Coffee Roastery</t>
+        </is>
+      </c>
+      <c r="E229" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F229" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G229" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ayed-adwan-8b530456</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>Ajmal Perfumes</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="inlineStr">
+        <is>
+          <t>https://ar-qa.ajmal.com/</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>Mohammad Tausif Salah</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>Head of E-Commerce, Ajmal Perfumes (GCC)</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G230" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/tausif-salah</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="5" t="inlineStr">
+        <is>
+          <t>Top Performance</t>
+        </is>
+      </c>
+      <c r="B231" s="6" t="inlineStr">
+        <is>
+          <t>https://topperformance.qa/</t>
+        </is>
+      </c>
+      <c r="C231" s="5" t="inlineStr">
+        <is>
+          <t>Yousef Najem</t>
+        </is>
+      </c>
+      <c r="D231" s="5" t="inlineStr">
+        <is>
+          <t>General Manager at Top Performance Qatar</t>
+        </is>
+      </c>
+      <c r="E231" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F231" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G231" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/yousef-najem</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>Black Tulip Flowers Qatar</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="inlineStr">
+        <is>
+          <t>https://www.blacktulipflowers.qa/</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>Mohamed Ehiya (M.M. Ehiya)</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>Owner &amp; Chairman, Black Tulip Group</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="5" t="inlineStr">
+        <is>
+          <t>Radio Suno 91.7 FM - No 1 Malayalam FM Radio in Qatar</t>
+        </is>
+      </c>
+      <c r="B233" s="6" t="inlineStr">
+        <is>
+          <t>https://suno.qa/</t>
+        </is>
+      </c>
+      <c r="C233" s="5" t="inlineStr">
+        <is>
+          <t>Muhammed Bashayir</t>
+        </is>
+      </c>
+      <c r="D233" s="5" t="inlineStr">
+        <is>
+          <t>Head of Marketing Communications, Olive Suno Radio Network (Radio Suno)</t>
+        </is>
+      </c>
+      <c r="E233" s="5" t="inlineStr">
+        <is>
+          <t>+974 44123133</t>
+        </is>
+      </c>
+      <c r="F233" s="5" t="inlineStr">
+        <is>
+          <t>media@olivesuno.com</t>
+        </is>
+      </c>
+      <c r="G233" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/muhammed-bashayir-882b6a1b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>Radio Suno 91.7 FM - No 1 Malayalam FM Radio in Qatar</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="inlineStr">
+        <is>
+          <t>https://suno.qa/</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>Ameer Ali</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder &amp; Managing Director, Olive Suno Radio Network / Radio Suno</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G234" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/ameer-ali-pv</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="5" t="inlineStr">
+        <is>
+          <t>Radio Suno 91.7 FM - No 1 Malayalam FM Radio in Qatar</t>
+        </is>
+      </c>
+      <c r="B235" s="6" t="inlineStr">
+        <is>
+          <t>https://suno.qa/</t>
+        </is>
+      </c>
+      <c r="C235" s="5" t="inlineStr">
+        <is>
+          <t>Krishnakumar Aiyappan</t>
+        </is>
+      </c>
+      <c r="D235" s="5" t="inlineStr">
+        <is>
+          <t>Co-Founder / Managing Director, Olive Suno Radio Network</t>
+        </is>
+      </c>
+      <c r="E235" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F235" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G235" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/krishnakumar-aiyappan-16ba4318</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>Tawreed</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="inlineStr">
+        <is>
+          <t>https://tawreed.qa/</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>Nasser K. Al Hamar</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>Founder, Tawreed (Alpina Group)</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="5" t="inlineStr">
+        <is>
+          <t>Chloe</t>
+        </is>
+      </c>
+      <c r="B237" s="6" t="inlineStr">
+        <is>
+          <t>https://www.chloe.com/en-qa/</t>
+        </is>
+      </c>
+      <c r="C237" s="5" t="inlineStr">
+        <is>
+          <t>Nagi Azar</t>
+        </is>
+      </c>
+      <c r="D237" s="5" t="inlineStr">
+        <is>
+          <t>Commercial Manager Middle East (Retail &amp; Wholesale), Chloé - Richemont</t>
+        </is>
+      </c>
+      <c r="E237" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F237" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G237" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nagi-azar-a1b88599</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>Ted Baker QAT</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tedbaker.qa/</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>Sanja Gorgieva</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>Regional Brand Manager - Ted Baker (MENA), Al-Futtaim</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G238" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/sanja-gorgieva-b912a087</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="5" t="inlineStr">
+        <is>
           <t>Gymshark</t>
         </is>
       </c>
-      <c r="B176" s="3" t="inlineStr">
+      <c r="B239" s="6" t="inlineStr">
         <is>
           <t>https://www.gymshark.qa/</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
+      <c r="C239" s="5" t="inlineStr">
+        <is>
+          <t>Sumit Srivastava</t>
+        </is>
+      </c>
+      <c r="D239" s="5" t="inlineStr">
+        <is>
+          <t>VP, CDO - Omnichannel Digital Innovation (Luxury Retail and Lifestyle), Al Tayer Insignia</t>
+        </is>
+      </c>
+      <c r="E239" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F239" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G239" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/sumitsrivastavaglobal</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>Gymshark</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gymshark.qa/</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>Pragya Singh</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>Digital Marketing Manager (Mamas &amp; Papas, Gymshark, Gap), Al Tayer Group</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G240" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/pragya-singh-aa428b29</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="5" t="inlineStr">
+        <is>
+          <t>Gymshark</t>
+        </is>
+      </c>
+      <c r="B241" s="6" t="inlineStr">
+        <is>
+          <t>https://www.gymshark.qa/</t>
+        </is>
+      </c>
+      <c r="C241" s="5" t="inlineStr">
         <is>
           <t>Awatef Airan</t>
         </is>
       </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="D241" s="5" t="inlineStr">
         <is>
           <t>Head of Product (Digital), Al Tayer Retail - incl. Gymshark</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="F176" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="G176" s="3" t="inlineStr">
+      <c r="E241" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F241" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G241" s="6" t="inlineStr">
         <is>
           <t>https://linkedin.com/in/awatef-airan-29708a114</t>
         </is>
       </c>
     </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>Startech Store</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="inlineStr">
+        <is>
+          <t>https://www.startechstore.com/</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>Shajeer Purayil</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>Business Owner / Founder &amp; MD, Star Tech Middle East WLL</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G242" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/shajeer-purayil-a367a73a</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G176"/>
+  <autoFilter ref="A1:G242"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -14479,152 +16924,268 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B95" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId173"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B96" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B97" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B97" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId189"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B105" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B106" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B107" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B108" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B109" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B110" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B111" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B112" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B113" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B115" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B117" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B118" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B119" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B120" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B121" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B122" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B123" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B124" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B125" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B126" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B127" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B128" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B129" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B130" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B131" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B132" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B133" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B134" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B135" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B136" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B137" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B106" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B107" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B108" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B109" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B110" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B111" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B112" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B113" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B115" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B117" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B118" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B119" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B120" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B121" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B122" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B123" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B124" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B125" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B126" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B127" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B128" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B129" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B130" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B131" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B132" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B133" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B134" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B135" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B136" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B137" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId250"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B138" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B139" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B139" r:id="rId253"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B140" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B141" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B142" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B143" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B144" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B145" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B146" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B147" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B148" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B149" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B150" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B151" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B152" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B153" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G153" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B154" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B155" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B156" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B157" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G157" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B158" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B159" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G159" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B160" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B161" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G161" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B162" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B163" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G163" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B164" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B165" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G165" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B166" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B167" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G167" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B168" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G168" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B169" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G169" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B170" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G170" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B171" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G171" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B172" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B173" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G173" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B174" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G174" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B175" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G175" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B176" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G176" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B141" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B142" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B143" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B144" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B145" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B146" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B147" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B148" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B149" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B150" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B151" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B152" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B153" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G153" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B154" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B155" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B156" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B157" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G157" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B158" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B159" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B160" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B161" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G161" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B162" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G162" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B163" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G163" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B164" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B165" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G165" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B166" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B167" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G167" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B168" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B169" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G169" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B170" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G170" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B171" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B172" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B173" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G173" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B174" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B175" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G175" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B176" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B177" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B178" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B179" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B180" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B181" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G181" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B182" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B183" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B184" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B185" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G185" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B186" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G186" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B187" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G187" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B188" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G188" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B189" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B190" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B191" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G191" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B192" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B193" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G193" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B194" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G194" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B195" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G195" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B196" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B197" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G197" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B198" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G198" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B199" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G199" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B200" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B201" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G201" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B202" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G202" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B203" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G203" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B204" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B205" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B206" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B207" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B208" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B209" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G209" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B210" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G210" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B211" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G211" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B212" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G212" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B213" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B214" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B215" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G215" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B216" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B217" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B218" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B219" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G219" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B220" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G220" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B221" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G221" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B222" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B223" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B224" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B225" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G225" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B226" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G226" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B227" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G227" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B228" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G228" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B229" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G229" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B230" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G230" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B231" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B232" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B233" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G233" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B234" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G234" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B235" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G235" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B236" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B237" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G237" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B238" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G238" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B239" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G239" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B240" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G240" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B241" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G241" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B242" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G242" r:id="rId436"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
